--- a/dados/xlsx/pivotante.xlsx
+++ b/dados/xlsx/pivotante.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/368431def48b862b/AGL/Automações/etiquetas/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E1A06DD-EE52-41A8-B472-2DDD6364CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E772419-DB1C-4567-B603-98D9618CB61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="1290" windowWidth="16200" windowHeight="9270" xr2:uid="{32F56DDD-ED7B-4F6D-AEF4-D608ECFB8CA7}"/>
+    <workbookView xWindow="28680" yWindow="1035" windowWidth="29040" windowHeight="15840" xr2:uid="{32F56DDD-ED7B-4F6D-AEF4-D608ECFB8CA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$121</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -95,9 +98,6 @@
     <t>P33 220V COM MOLA E SEM FIM BV 2 ENT</t>
   </si>
   <si>
-    <t>12UF</t>
-  </si>
-  <si>
     <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V - 0,75M</t>
   </si>
   <si>
@@ -512,9 +512,6 @@
     <t>P33 COM MOLA E SEM FIM BV 2 ENT</t>
   </si>
   <si>
-    <t xml:space="preserve">12UF </t>
-  </si>
-  <si>
     <t>CONJUNTO MOVIMENTADOR INTELIGENTE IZZY TRINO PIVÔ 3 220V - 1M - DUPLO EX</t>
   </si>
   <si>
@@ -522,6 +519,12 @@
   </si>
   <si>
     <t>CONJUNTO MOVIMENTADOR INTELIGENTE IZZY TRINO PIVÔ 3 220V - 0,75M - DUPLO EX</t>
+  </si>
+  <si>
+    <t>15UF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15UF </t>
   </si>
 </sst>
 </file>
@@ -1091,6 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1528DE62-AD50-4187-86F3-565BB382A7C2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1125,7 +1129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2004036</v>
       </c>
@@ -1148,7 +1152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2004038</v>
       </c>
@@ -1171,7 +1175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2007001</v>
       </c>
@@ -1211,18 +1215,18 @@
         <v>17</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2007003</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
@@ -1245,7 +1249,7 @@
         <v>2007004</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -1257,18 +1261,18 @@
         <v>17</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2007005</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
@@ -1291,7 +1295,7 @@
         <v>2007006</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>8</v>
@@ -1303,18 +1307,18 @@
         <v>17</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2007007</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>8</v>
@@ -1337,7 +1341,7 @@
         <v>2007008</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>8</v>
@@ -1349,18 +1353,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2007009</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>8</v>
@@ -1383,30 +1387,30 @@
         <v>2007010</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2007011</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>8</v>
@@ -1429,7 +1433,7 @@
         <v>2007012</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>8</v>
@@ -1438,21 +1442,21 @@
         <v>9</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2007013</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>8</v>
@@ -1475,7 +1479,7 @@
         <v>2007014</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>8</v>
@@ -1484,21 +1488,21 @@
         <v>9</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2007015</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>8</v>
@@ -1521,7 +1525,7 @@
         <v>2007016</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>8</v>
@@ -1530,24 +1534,24 @@
         <v>9</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2007017</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
@@ -1559,7 +1563,7 @@
         <v>11</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1567,10 +1571,10 @@
         <v>2007018</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>9</v>
@@ -1579,21 +1583,21 @@
         <v>17</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2007019</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>9</v>
@@ -1605,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1613,10 +1617,10 @@
         <v>2007020</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>9</v>
@@ -1625,21 +1629,21 @@
         <v>17</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>2007021</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -1651,7 +1655,7 @@
         <v>11</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1659,10 +1663,10 @@
         <v>2007022</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>9</v>
@@ -1671,21 +1675,21 @@
         <v>17</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2007023</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>9</v>
@@ -1697,7 +1701,7 @@
         <v>11</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1705,10 +1709,10 @@
         <v>2007024</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>9</v>
@@ -1717,21 +1721,21 @@
         <v>17</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2007025</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>9</v>
@@ -1743,7 +1747,7 @@
         <v>11</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1751,33 +1755,33 @@
         <v>2007026</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2007027</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>9</v>
@@ -1789,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1797,33 +1801,33 @@
         <v>2007028</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2007029</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>9</v>
@@ -1835,7 +1839,7 @@
         <v>11</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1843,33 +1847,33 @@
         <v>2007030</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2007031</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>9</v>
@@ -1881,7 +1885,7 @@
         <v>11</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1889,30 +1893,30 @@
         <v>2007032</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>2007055</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>8</v>
@@ -1935,7 +1939,7 @@
         <v>2007056</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>8</v>
@@ -1944,10 +1948,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>12</v>
@@ -1958,30 +1962,30 @@
         <v>2007058</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>2007059</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>8</v>
@@ -2004,7 +2008,7 @@
         <v>2007060</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>8</v>
@@ -2016,7 +2020,7 @@
         <v>17</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>12</v>
@@ -2027,10 +2031,10 @@
         <v>2007063</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>9</v>
@@ -2039,10 +2043,10 @@
         <v>17</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,30 +2054,30 @@
         <v>2007065</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="F42" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>2009001</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>8</v>
@@ -2088,7 +2092,7 @@
         <v>11</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2096,7 +2100,7 @@
         <v>2009002</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>8</v>
@@ -2108,18 +2112,18 @@
         <v>17</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>2009003</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>8</v>
@@ -2134,7 +2138,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2142,7 +2146,7 @@
         <v>2009004</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>8</v>
@@ -2151,24 +2155,24 @@
         <v>9</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>2007070</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>9</v>
@@ -2180,18 +2184,18 @@
         <v>11</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>2007071</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>9</v>
@@ -2203,18 +2207,18 @@
         <v>11</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>2007072</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>9</v>
@@ -2226,7 +2230,7 @@
         <v>11</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2234,33 +2238,33 @@
         <v>2009005</v>
       </c>
       <c r="B50" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>2007035</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>9</v>
@@ -2272,18 +2276,18 @@
         <v>11</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>2007037</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>9</v>
@@ -2295,7 +2299,7 @@
         <v>11</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2303,22 +2307,22 @@
         <v>2007073</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="F53" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2326,22 +2330,22 @@
         <v>2007038</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2349,22 +2353,22 @@
         <v>2007044</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="F55" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,7 +2376,7 @@
         <v>2007049</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>8</v>
@@ -2381,10 +2385,10 @@
         <v>9</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>12</v>
@@ -2395,7 +2399,7 @@
         <v>2007052</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>8</v>
@@ -2404,24 +2408,24 @@
         <v>9</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>2007043</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>9</v>
@@ -2433,7 +2437,7 @@
         <v>11</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2441,7 +2445,7 @@
         <v>2007050</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>8</v>
@@ -2450,10 +2454,10 @@
         <v>9</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>12</v>
@@ -2464,22 +2468,22 @@
         <v>2007036</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2487,7 +2491,7 @@
         <v>2007078</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>8</v>
@@ -2496,30 +2500,30 @@
         <v>9</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2002005</v>
       </c>
       <c r="B62" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>11</v>
@@ -2531,56 +2535,56 @@
         <v>2002006</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="F63" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>2002007</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="F64" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2002010</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>11</v>
@@ -2591,36 +2595,36 @@
         <v>2002011</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>2008001</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>11</v>
@@ -2631,36 +2635,36 @@
         <v>2008002</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>2008003</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>11</v>
@@ -2671,56 +2675,56 @@
         <v>2008004</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>2008005</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>2008007</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>11</v>
@@ -2731,36 +2735,36 @@
         <v>2008008</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>2008011</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>11</v>
@@ -2771,36 +2775,36 @@
         <v>2008012</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>2008013</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>11</v>
@@ -2811,36 +2815,36 @@
         <v>2008014</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>2008015</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>11</v>
@@ -2851,36 +2855,36 @@
         <v>2008016</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>2008017</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>11</v>
@@ -2891,19 +2895,19 @@
         <v>2008018</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2911,19 +2915,19 @@
         <v>2008040</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -2931,36 +2935,36 @@
         <v>2008046</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>2008056</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>11</v>
@@ -2971,36 +2975,36 @@
         <v>2008057</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>2008058</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>11</v>
@@ -3011,36 +3015,36 @@
         <v>2008059</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13">
         <v>2008060</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>11</v>
@@ -3051,36 +3055,36 @@
         <v>2008061</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>2013003</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>11</v>
@@ -3091,19 +3095,19 @@
         <v>2008022</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="F91" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G91" s="8">
         <v>0</v>
@@ -3114,39 +3118,39 @@
         <v>2008025</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="F92" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G92" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>2013001</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>11</v>
@@ -3157,22 +3161,22 @@
         <v>2007042</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -3180,19 +3184,19 @@
         <v>2013002</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -3200,19 +3204,19 @@
         <v>2013004</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,19 +3224,19 @@
         <v>2013005</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G97" s="8">
         <v>0</v>
@@ -3243,19 +3247,19 @@
         <v>2008024</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G98" s="8">
         <v>0</v>
@@ -3266,33 +3270,33 @@
         <v>2001156</v>
       </c>
       <c r="B99" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E99" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="F99" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G99" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>2007084</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>9</v>
@@ -3304,7 +3308,7 @@
         <v>11</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,54 +3316,54 @@
         <v>2007085</v>
       </c>
       <c r="B101" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="F101" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>813461</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17">
         <v>813459</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17">
         <v>813460</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17">
         <v>813458</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3367,39 +3371,39 @@
         <v>2007077</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="F106" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>2007086</v>
       </c>
       <c r="B107" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>11</v>
@@ -3408,27 +3412,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>2007087</v>
       </c>
       <c r="B108" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="D108" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -3436,19 +3440,19 @@
         <v>2007088</v>
       </c>
       <c r="B109" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="F109" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>12</v>
@@ -3459,39 +3463,39 @@
         <v>2007089</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>2007090</v>
       </c>
       <c r="B111" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>11</v>
@@ -3500,27 +3504,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>2007091</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -3528,19 +3532,19 @@
         <v>2007092</v>
       </c>
       <c r="B113" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>150</v>
-      </c>
       <c r="F113" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>12</v>
@@ -3551,43 +3555,43 @@
         <v>2007093</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>2007091</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>813465</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>813464</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -3595,22 +3599,22 @@
         <v>2007097</v>
       </c>
       <c r="B118" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="D118" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="F118" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -3618,7 +3622,7 @@
         <v>2009014</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>8</v>
@@ -3627,13 +3631,13 @@
         <v>9</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -3641,22 +3645,22 @@
         <v>2007101</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -3664,25 +3668,32 @@
         <v>2007100</v>
       </c>
       <c r="B121" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F121" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>157</v>
-      </c>
       <c r="G121" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G121" xr:uid="{1528DE62-AD50-4187-86F3-565BB382A7C2}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="12UF"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>